--- a/data/pbn_procedures.xlsx
+++ b/data/pbn_procedures.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oburdash\dev\repos\standard_inputs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C55719-FE3C-4B8B-ACA3-298B4AD227AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31283E81-EA10-4F40-9E13-D56059AC28DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pbn_deployment" sheetId="1" r:id="rId1"/>
@@ -52,18 +52,9 @@
     <t>RNP APCH to LPV</t>
   </si>
   <si>
-    <t>Any RNP APCH (LNAV or LNAV/VNAV or LPV)</t>
-  </si>
-  <si>
     <t>RNP AR APCH</t>
   </si>
   <si>
-    <t>ILS (all, see breakdown below)</t>
-  </si>
-  <si>
-    <t>3D (ILS Cat I or ILS Cat II/II or APV)</t>
-  </si>
-  <si>
     <t>GLS</t>
   </si>
   <si>
@@ -73,13 +64,22 @@
     <t>runway_share</t>
   </si>
   <si>
-    <t>ILS Cat I (and no Cat II/III)</t>
-  </si>
-  <si>
-    <t>ILS Cat II/III</t>
-  </si>
-  <si>
     <t>runway_nb</t>
+  </si>
+  <si>
+    <t>ILS</t>
+  </si>
+  <si>
+    <t>ILS Cat 1 Only</t>
+  </si>
+  <si>
+    <t>ILS Cat 2/3</t>
+  </si>
+  <si>
+    <t>Any PBN (RNP APCH or RNP AR APCH)</t>
+  </si>
+  <si>
+    <t>PA (LPV CAT 1 or ILS or GLS)</t>
   </si>
 </sst>
 </file>
@@ -407,13 +407,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -421,10 +421,10 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>1154</v>
+        <v>1282</v>
       </c>
       <c r="C2">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -432,10 +432,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>833</v>
+        <v>974</v>
       </c>
       <c r="C3">
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -443,51 +443,51 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>754</v>
+        <v>885</v>
       </c>
       <c r="C4">
-        <v>0.46</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B5">
-        <v>1173</v>
+        <v>1297</v>
       </c>
       <c r="C5">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="C6">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="C7">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C8">
         <v>0.02</v>
@@ -495,13 +495,13 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B9">
-        <v>948</v>
+        <v>1006</v>
       </c>
       <c r="C9">
-        <v>0.57999999999999996</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -521,32 +521,32 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="C2">
-        <v>0.313</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="C3">
         <v>0.16</v>
@@ -555,4 +555,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{fd60f3b8-f236-4830-aecc-da0a7fc54679}" enabled="1" method="Standard" siteId="{76f33c20-5979-4408-adf7-8b3c4be95e52}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>